--- a/public/template-siswa.xlsx
+++ b/public/template-siswa.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\SIMPRESI\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Project\Bella\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45FDF50F-27C3-4D70-897A-2312AC9CEB48}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8614746-20D3-432C-96D8-6366B86824CE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5517E238-0078-4709-A735-F18CA9B03405}"/>
+    <workbookView xWindow="1632" yWindow="2148" windowWidth="17280" windowHeight="8880" xr2:uid="{5517E238-0078-4709-A735-F18CA9B03405}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
   <si>
     <t>nisn</t>
   </si>
@@ -69,16 +69,76 @@
     <t>7A</t>
   </si>
   <si>
-    <t>Bella</t>
-  </si>
-  <si>
-    <t>nama_orang_tua</t>
+    <t>tempat_lahir</t>
+  </si>
+  <si>
+    <t>tanggal_lahir</t>
+  </si>
+  <si>
+    <t>agama</t>
+  </si>
+  <si>
+    <t>nama_ayah</t>
+  </si>
+  <si>
+    <t>no_hp_ayah</t>
+  </si>
+  <si>
+    <t>pekerjaan_ayah</t>
+  </si>
+  <si>
+    <t>nama_ibu</t>
+  </si>
+  <si>
+    <t>no_hp_ibu</t>
+  </si>
+  <si>
+    <t>pekerjaan_ibu</t>
+  </si>
+  <si>
+    <t>nama_wali</t>
+  </si>
+  <si>
+    <t>no_hp_wali</t>
+  </si>
+  <si>
+    <t>email_wali</t>
+  </si>
+  <si>
+    <t>pekerjaan_wali</t>
+  </si>
+  <si>
+    <t>alamat_orang_tua</t>
+  </si>
+  <si>
+    <t>Islam</t>
+  </si>
+  <si>
+    <t>Jl Mawar No 1</t>
+  </si>
+  <si>
+    <t>Budi Saputra</t>
+  </si>
+  <si>
+    <t>Wiraswasta</t>
+  </si>
+  <si>
+    <t>Siti Aminah</t>
+  </si>
+  <si>
+    <t>Ibu Rumah Tangga</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -127,10 +187,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -445,21 +507,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E14964B2-E838-4E50-B732-E31C1B3EB631}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="2"/>
+    <col min="5" max="5" width="13.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="18.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -473,24 +548,63 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>13</v>
+      <c r="K1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1234567890</v>
       </c>
       <c r="B2" s="2">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>7</v>
@@ -498,17 +612,56 @@
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="4">
+        <v>41039</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>12</v>
+      <c r="K2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="2">
+        <v>8123456789</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" s="2">
+        <v>8123456788</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
